--- a/Documentation/classes_inscription/class_Player.xlsx
+++ b/Documentation/classes_inscription/class_Player.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\classes_inscription\classes_inscription\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AeroData\main_for_all\python\MathUp\Documentation\classes_inscription\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A174DBB-F3CB-4EBF-B241-607462FD373A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA3C926-6EDF-4BA1-A2B2-1E88B8339A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>תכונות(שדות)</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>מעדכנת את  משתנה animation_index בהתאם ל animation_speed ומעדכנת את מראה חיצוני(image, animation)</t>
+  </si>
+  <si>
+    <t>double_jump</t>
+  </si>
+  <si>
+    <t>שומר ארך bool שמייצג האם יש לשחקן אפשרות לקפיצה שנייה</t>
   </si>
 </sst>
 </file>
@@ -201,7 +207,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -297,11 +303,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -314,9 +333,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -332,9 +348,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -612,33 +632,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7265625" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" customWidth="1"/>
+    <col min="4" max="4" width="30.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="12"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -652,7 +672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -662,11 +682,11 @@
       <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -680,7 +700,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -694,7 +714,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -708,7 +728,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
@@ -722,7 +742,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -736,7 +756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -750,7 +770,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -764,7 +784,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -778,7 +798,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -788,7 +808,7 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -798,7 +818,7 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -808,11 +828,22 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
+    <row r="16" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
